--- a/data/trans_bre/P19C03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C03-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 5,6</t>
+          <t>-2,74; 5,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 8,17</t>
+          <t>0,29; 7,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 7,5</t>
+          <t>-2,73; 7,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 3,33</t>
+          <t>-3,98; 3,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 29,91</t>
+          <t>-11,48; 31,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 48,2</t>
+          <t>1,26; 45,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 43,6</t>
+          <t>-12,49; 41,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 27,0</t>
+          <t>-22,75; 26,78</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 5,15</t>
+          <t>-2,64; 4,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 2,19</t>
+          <t>-4,02; 2,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 1,97</t>
+          <t>-4,71; 1,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 6,87</t>
+          <t>-6,23; 6,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 14,52</t>
+          <t>-6,75; 14,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 6,64</t>
+          <t>-11,42; 9,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 6,83</t>
+          <t>-14,64; 6,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,47; 44,69</t>
+          <t>-29,42; 36,71</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 6,4</t>
+          <t>-6,52; 5,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 0,97</t>
+          <t>-12,72; 0,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 1,87</t>
+          <t>-8,78; 1,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 5,38</t>
+          <t>-2,38; 5,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 23,1</t>
+          <t>-19,04; 20,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,62; 3,74</t>
+          <t>-35,45; 3,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-31,45; 8,75</t>
+          <t>-31,49; 8,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 38,1</t>
+          <t>-12,66; 37,43</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,75</t>
+          <t>-2,58; 2,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,13</t>
+          <t>-3,61; 1,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 1,06</t>
+          <t>-4,01; 1,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 3,9</t>
+          <t>-3,83; 4,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 9,06</t>
+          <t>-7,8; 9,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 3,87</t>
+          <t>-11,44; 4,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 4,13</t>
+          <t>-13,63; 3,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 23,18</t>
+          <t>-19,53; 27,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C03-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-2,22%</t>
+          <t>-6,79%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 5,93</t>
+          <t>-2,56; 5,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 7,98</t>
+          <t>0,7; 8,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 7,1</t>
+          <t>-3,01; 6,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 3,26</t>
+          <t>-5,3; 2,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 31,75</t>
+          <t>-11,05; 30,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 45,97</t>
+          <t>2,99; 45,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 41,59</t>
+          <t>-13,75; 38,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 26,78</t>
+          <t>-28,51; 20,17</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,83</t>
+          <t>-1,74</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-4,35%</t>
+          <t>-8,26%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 4,99</t>
+          <t>-2,33; 5,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 2,97</t>
+          <t>-4,54; 2,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 1,88</t>
+          <t>-4,31; 2,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 6,34</t>
+          <t>-4,66; 0,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 14,35</t>
+          <t>-6,01; 15,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 9,33</t>
+          <t>-12,63; 6,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 6,48</t>
+          <t>-13,7; 7,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,42; 36,71</t>
+          <t>-20,61; 3,96</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>3,49</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 5,89</t>
+          <t>-6,56; 6,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 0,8</t>
+          <t>-12,1; 0,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 1,81</t>
+          <t>-9,46; 1,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 5,5</t>
+          <t>-1,35; 7,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 20,51</t>
+          <t>-19,12; 22,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 3,53</t>
+          <t>-33,92; 2,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 8,45</t>
+          <t>-33,14; 7,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 37,43</t>
+          <t>-7,35; 51,66</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-2,88%</t>
+          <t>-4,33%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,75</t>
+          <t>-2,38; 2,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,34</t>
+          <t>-3,31; 1,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,01</t>
+          <t>-3,87; 0,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 4,16</t>
+          <t>-2,77; 1,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 9,03</t>
+          <t>-7,27; 9,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 4,76</t>
+          <t>-10,72; 4,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 3,86</t>
+          <t>-13,33; 3,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 27,02</t>
+          <t>-13,26; 6,62</t>
         </is>
       </c>
     </row>
